--- a/考研复习计划表模板 --地硕.xlsx
+++ b/考研复习计划表模板 --地硕.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\错题集\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12790"/>
+    <workbookView windowWidth="24750" windowHeight="12340"/>
   </bookViews>
   <sheets>
     <sheet name="月计划模版" sheetId="3" r:id="rId1"/>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="66">
   <si>
     <t>月份</t>
   </si>
@@ -80,25 +85,79 @@
 3、不定积分660</t>
   </si>
   <si>
+    <t>第六周：导数+中值定理</t>
+  </si>
+  <si>
     <t>英语</t>
   </si>
   <si>
     <t>总目标：开始背考研核心词和刷阅读真题</t>
   </si>
   <si>
+    <t>第五周：核心词14-16；14年15年真题</t>
+  </si>
+  <si>
+    <t>第六周：核心词1-13；16-18年真题</t>
+  </si>
+  <si>
     <t>政治</t>
   </si>
   <si>
-    <t>总目标：过第一轮马原和新思想</t>
+    <t>总目标：过第一轮马原和新思想熟悉框架</t>
   </si>
   <si>
     <t>/</t>
   </si>
   <si>
+    <t>第五周：政治经济学＋新思想概述</t>
+  </si>
+  <si>
+    <t>第六周：新思想二三、四五、六七、八九、十十一十二、十七</t>
+  </si>
+  <si>
     <t>8月</t>
   </si>
   <si>
     <t>总目标：争取结束高数强化</t>
+  </si>
+  <si>
+    <r>
+      <t>第七周：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF800080"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>积分概念、计算和积分不等式</t>
+    </r>
+  </si>
+  <si>
+    <t>第八周：多元微分、二重积分</t>
+  </si>
+  <si>
+    <t>第九周：微分方程、导数物理应用、积分几何物理应用</t>
+  </si>
+  <si>
+    <t>第十周：</t>
+  </si>
+  <si>
+    <t>总目标：完成第一轮词汇和阅读真题，完善语法知识</t>
+  </si>
+  <si>
+    <t>第七周：核心词1-10；19-21年真题</t>
+  </si>
+  <si>
+    <t>第八周：核心词11-20；07-13年真题</t>
+  </si>
+  <si>
+    <t>第九周：核心词21-30；</t>
+  </si>
+  <si>
+    <t>总目标：史纲和毛概</t>
   </si>
   <si>
     <t>9月</t>
@@ -198,7 +257,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,8 +473,15 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="49">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -454,37 +520,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="3" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -926,7 +968,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -950,16 +992,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -968,13 +1010,25 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1037,20 +1091,8 @@
     <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1105,103 +1147,100 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1537,7 +1576,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="57.7727272727273" customWidth="1"/>
@@ -1566,10 +1605,10 @@
       <c r="A2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="19"/>
@@ -1577,8 +1616,8 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="21" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="22" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="19"/>
@@ -1586,7 +1625,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
+      <c r="B4" s="21"/>
       <c r="C4" s="19" t="s">
         <v>9</v>
       </c>
@@ -1595,7 +1634,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="19" t="s">
         <v>10</v>
       </c>
@@ -1604,7 +1643,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20"/>
-      <c r="B6" s="22"/>
+      <c r="B6" s="23"/>
       <c r="C6" s="19" t="s">
         <v>11</v>
       </c>
@@ -1613,7 +1652,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="20"/>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="17" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="24" t="s">
@@ -1624,8 +1663,8 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="20"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="26" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="25"/>
@@ -1633,8 +1672,8 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="20"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="28" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="25"/>
@@ -1642,8 +1681,8 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="20"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="28" t="s">
+      <c r="B10" s="20"/>
+      <c r="C10" s="24" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="25"/>
@@ -1651,8 +1690,8 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="20"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="28" t="s">
+      <c r="B11" s="20"/>
+      <c r="C11" s="24" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="25"/>
@@ -1660,300 +1699,425 @@
     </row>
     <row r="12" ht="42" spans="1:5">
       <c r="A12" s="20"/>
-      <c r="B12" s="29"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="27" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="25"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="20"/>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="D13" s="27"/>
+      <c r="E13" s="25"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="20"/>
+      <c r="B14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="22"/>
-      <c r="B14" s="34" t="s">
+      <c r="C14" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="20"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="37" t="s">
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="20"/>
+      <c r="B17" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="C17" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="20"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="30"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C20" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="37"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="37"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="37"/>
-      <c r="B20" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>20</v>
-      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="18"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="22"/>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="40"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>24</v>
+      <c r="A23" s="35"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="D23" s="25"/>
       <c r="E23" s="25"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="27"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="24" t="s">
+        <v>29</v>
+      </c>
       <c r="D24" s="25"/>
       <c r="E24" s="25"/>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="40"/>
-      <c r="B25" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
+    <row r="25" ht="42" spans="1:5">
+      <c r="A25" s="35"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="25"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="40"/>
-      <c r="B26" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>20</v>
-      </c>
+      <c r="A26" s="35"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="27"/>
+      <c r="E26" s="25"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="44" t="s">
+      <c r="A27" s="35"/>
+      <c r="B27" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="35"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="35"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="35"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="35"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="35"/>
+      <c r="B32" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="45"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="45"/>
-      <c r="B29" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="45"/>
-      <c r="B31" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="45"/>
-      <c r="B32" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="35" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="B33" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>27</v>
-      </c>
+      <c r="C33" s="19"/>
       <c r="D33" s="19"/>
       <c r="E33" s="19"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="49"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="21"/>
+      <c r="A34" s="41"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="22"/>
       <c r="D34" s="19"/>
       <c r="E34" s="19"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="49"/>
-      <c r="B35" s="47" t="s">
+      <c r="A35" s="41"/>
+      <c r="B35" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
+      <c r="C35" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="49"/>
-      <c r="B36" s="49"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
+      <c r="A36" s="41"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="49"/>
-      <c r="B37" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
+      <c r="A37" s="41"/>
+      <c r="B37" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="28"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="49"/>
-      <c r="B38" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="35" t="s">
-        <v>20</v>
+      <c r="A38" s="41"/>
+      <c r="B38" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="44"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="44"/>
+      <c r="B41" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="24"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="44"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="44"/>
+      <c r="B43" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="44"/>
+      <c r="B44" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="47"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="47"/>
+      <c r="B47" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="47"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="47"/>
+      <c r="B49" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="47"/>
+      <c r="B50" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="32" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A2:A14"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="A27:A32"/>
+  <mergeCells count="18">
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A20:A32"/>
     <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A39:A44"/>
+    <mergeCell ref="A45:A50"/>
     <mergeCell ref="B2:B6"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="B27:B31"/>
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B47:B48"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" location="'3月第一周'!A1" display="第一周："/>
@@ -1979,7 +2143,7 @@
   <sheetData>
     <row r="1" ht="27.5" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1993,7 +2157,7 @@
     </row>
     <row r="2" ht="28" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2007,7 +2171,7 @@
     </row>
     <row r="3" customFormat="1" ht="28" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4"/>
@@ -2021,10 +2185,10 @@
     </row>
     <row r="4" customFormat="1" spans="1:10">
       <c r="A4" s="6" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>6</v>
@@ -2041,7 +2205,7 @@
       <c r="A5" s="6"/>
       <c r="B5" s="2"/>
       <c r="C5" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -2069,7 +2233,7 @@
       <c r="A7" s="6"/>
       <c r="B7" s="2"/>
       <c r="C7" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2082,58 +2246,58 @@
     <row r="8" customFormat="1" spans="1:10">
       <c r="A8" s="6"/>
       <c r="B8" s="9" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="6"/>
       <c r="B9" s="11" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="J9" s="13"/>
     </row>
@@ -2141,25 +2305,25 @@
       <c r="A10" s="6"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J10" s="13"/>
     </row>
@@ -2167,25 +2331,25 @@
       <c r="A11" s="6"/>
       <c r="B11" s="11"/>
       <c r="C11" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="J11" s="13"/>
     </row>
@@ -2193,25 +2357,25 @@
       <c r="A12" s="6"/>
       <c r="B12" s="11"/>
       <c r="C12" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J12" s="13"/>
     </row>
@@ -2219,53 +2383,53 @@
       <c r="A13" s="6"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="J13" s="13"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="6"/>
       <c r="B14" s="11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="J14" s="6"/>
     </row>
@@ -2273,25 +2437,25 @@
       <c r="A15" s="6"/>
       <c r="B15" s="11"/>
       <c r="C15" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J15" s="6"/>
     </row>
@@ -2299,25 +2463,25 @@
       <c r="A16" s="6"/>
       <c r="B16" s="11"/>
       <c r="C16" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="J16" s="6"/>
     </row>
@@ -2325,25 +2489,25 @@
       <c r="A17" s="6"/>
       <c r="B17" s="11"/>
       <c r="C17" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -2351,53 +2515,53 @@
       <c r="A18" s="6"/>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="J18" s="6"/>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="6"/>
       <c r="B19" s="11" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="J19" s="6"/>
     </row>
@@ -2405,25 +2569,25 @@
       <c r="A20" s="6"/>
       <c r="B20" s="11"/>
       <c r="C20" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J20" s="6"/>
     </row>
@@ -2431,25 +2595,25 @@
       <c r="A21" s="6"/>
       <c r="B21" s="11"/>
       <c r="C21" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="J21" s="6"/>
     </row>
@@ -2457,25 +2621,25 @@
       <c r="A22" s="6"/>
       <c r="B22" s="11"/>
       <c r="C22" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J22" s="6"/>
     </row>
@@ -2483,53 +2647,53 @@
       <c r="A23" s="6"/>
       <c r="B23" s="11"/>
       <c r="C23" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="J23" s="6"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="6"/>
       <c r="B24" s="11" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="J24" s="6"/>
     </row>
@@ -2537,25 +2701,25 @@
       <c r="A25" s="6"/>
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J25" s="6"/>
     </row>
@@ -2563,25 +2727,25 @@
       <c r="A26" s="6"/>
       <c r="B26" s="11"/>
       <c r="C26" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="J26" s="6"/>
     </row>
@@ -2589,25 +2753,25 @@
       <c r="A27" s="6"/>
       <c r="B27" s="11"/>
       <c r="C27" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J27" s="6"/>
     </row>
@@ -2615,32 +2779,32 @@
       <c r="A28" s="6"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="J28" s="6"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="6"/>
       <c r="B29" s="14" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>

--- a/考研复习计划表模板 --地硕.xlsx
+++ b/考研复习计划表模板 --地硕.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12340"/>
+    <workbookView windowWidth="11950" windowHeight="12350"/>
   </bookViews>
   <sheets>
     <sheet name="月计划模版" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="66">
   <si>
     <t>月份</t>
   </si>
@@ -112,7 +112,7 @@
     <t>第五周：政治经济学＋新思想概述</t>
   </si>
   <si>
-    <t>第六周：新思想二三、四五、六七、八九、十十一十二、十七</t>
+    <t>第六周：新思想二三四五、六七、八九、十十一十二、十七</t>
   </si>
   <si>
     <t>8月</t>
@@ -1092,7 +1092,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1147,18 +1147,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1183,9 +1177,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1199,12 +1190,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1576,7 +1561,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="57.7727272727273" customWidth="1"/>
@@ -1605,519 +1590,509 @@
       <c r="A2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22" t="s">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="19" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="19" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="20"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="19" t="s">
+      <c r="A6" s="19"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="20"/>
+      <c r="A7" s="19"/>
       <c r="B7" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="26" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="24" t="s">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="24" t="s">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="24" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
     </row>
     <row r="12" ht="42" spans="1:5">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="25" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="25"/>
+      <c r="E12" s="23"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="25" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="23"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="20"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="28" t="s">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="20"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="28" t="s">
+      <c r="A16" s="19"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="20"/>
-      <c r="B17" s="31" t="s">
+      <c r="A17" s="19"/>
+      <c r="B17" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="33" t="s">
+      <c r="D17" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="30" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="20"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="32" t="s">
+      <c r="A18" s="19"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="33" t="s">
+      <c r="D18" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="30"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="32" t="s">
+      <c r="A19" s="21"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="33" t="s">
+      <c r="D19" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="30" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="35"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="35"/>
-      <c r="B22" s="38" t="s">
+      <c r="A22" s="32"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="32"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="32"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="25"/>
+      <c r="E24" s="23"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="32"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="25"/>
+      <c r="E25" s="23"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="32"/>
+      <c r="B26" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="32"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="32"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="32"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="32"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="32"/>
+      <c r="B31" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="36"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="36"/>
+      <c r="B34" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="35"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="35"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-    </row>
-    <row r="25" ht="42" spans="1:5">
-      <c r="A25" s="35"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="25"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="35"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="25"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="35"/>
-      <c r="B27" s="38" t="s">
+      <c r="C34" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="36"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="36"/>
+      <c r="B36" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="35"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="35"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="35"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="35"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="35"/>
-      <c r="B32" s="35" t="s">
+      <c r="C36" s="26"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="36"/>
+      <c r="B37" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" s="33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="42" t="s">
+      <c r="C37" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="41"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="41"/>
-      <c r="B35" s="41" t="s">
+      <c r="C38" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="39"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="39"/>
+      <c r="B40" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="41"/>
-      <c r="B36" s="41"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="41"/>
-      <c r="B37" s="41" t="s">
+      <c r="C40" s="22"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="39"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="39"/>
+      <c r="B42" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="41"/>
-      <c r="B38" s="41" t="s">
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="39"/>
+      <c r="B43" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" s="33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="44" t="s">
+      <c r="C43" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="45" t="s">
+      <c r="B44" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="44"/>
-      <c r="B40" s="46"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="44"/>
-      <c r="B41" s="44" t="s">
+      <c r="C44" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="42"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="42"/>
+      <c r="B46" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="24"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="44"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="44"/>
-      <c r="B43" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="44"/>
-      <c r="B44" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="C44" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" s="32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="47"/>
-      <c r="B46" s="49"/>
       <c r="C46" s="22"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="47"/>
-      <c r="B47" s="47" t="s">
-        <v>12</v>
-      </c>
+      <c r="A47" s="42"/>
+      <c r="B47" s="42"/>
       <c r="C47" s="24"/>
       <c r="D47" s="24"/>
       <c r="E47" s="24"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="47"/>
-      <c r="B48" s="47"/>
+      <c r="A48" s="42"/>
+      <c r="B48" s="42" t="s">
+        <v>17</v>
+      </c>
       <c r="C48" s="26"/>
       <c r="D48" s="26"/>
       <c r="E48" s="26"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="47"/>
-      <c r="B49" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="47"/>
-      <c r="B50" s="47" t="s">
+      <c r="A49" s="42"/>
+      <c r="B49" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E50" s="32" t="s">
+      <c r="C49" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="29" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="17">
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A20:A32"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="A39:A44"/>
-    <mergeCell ref="A45:A50"/>
+    <mergeCell ref="A20:A31"/>
+    <mergeCell ref="A32:A37"/>
+    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A44:A49"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="B7:B13"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B21:B25"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B46:B47"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" location="'3月第一周'!A1" display="第一周："/>
